--- a/mappings/parameter_e_h_g.xlsx
+++ b/mappings/parameter_e_h_g.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="donar_isc_cas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nomatch_donar_isc_cas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wadar_isc_cas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nomatch_wadar_isc_cas" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,42 +472,42 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>DONAR_Parameter</t>
+          <t>grootheid_code</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>DONAR_PARCode</t>
+          <t>wadar_PARCode</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>HDH</t>
+          <t>hoedanigheid_code</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1101</v>
+        <v>1083</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15972-60-8</t>
+          <t>2921-88-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alCl</t>
+          <t>C2yClprfs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>alachloor</t>
+          <t>ethylchloorpyrifos</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alachloor</t>
+          <t>Chloorpyrifos (Chloorpyrifos ethyl)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>alachloor</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>alCl</t>
+          <t>C2yClprfs</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -543,26 +543,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>309-00-2</t>
+          <t>15972-60-8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>aldn</t>
+          <t>alCl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>aldrin</t>
+          <t>alachloor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aldrin</t>
+          <t>Alachloor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -582,12 +582,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>aldrin</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>aldn</t>
+          <t>alCl</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,26 +598,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1912-24-9</t>
+          <t>309-00-2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atzne</t>
+          <t>aldn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>atrazine</t>
+          <t>aldrin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atrazine</t>
+          <t>Aldrin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>atrazine</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>atzne</t>
+          <t>aldn</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>atrazine</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -708,26 +708,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>71-43-2</t>
+          <t>1912-24-9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>atzne</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>benzeen</t>
+          <t>atrazine</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Benzeen</t>
+          <t>Atrazine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>benzeen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>atzne</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -763,26 +763,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50-32-8</t>
+          <t>71-43-2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BaP</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>benzo(a)pyreen</t>
+          <t>benzeen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Benzo (a) pyreen</t>
+          <t>Benzeen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>benzo(a)pyreen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BaP</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>benzo(a)pyreen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -867,32 +867,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>207-08-9</t>
+          <t>50-32-8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BkF</t>
+          <t>BaP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>benzo(k)fluorantheen</t>
+          <t>benzo(a)pyreen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Benzo (k) fluorantheen</t>
+          <t>Benzo (a) pyreen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>benzo(k)fluorantheen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BkF</t>
+          <t>BaP</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>benzo(k)fluorantheen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -977,32 +977,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>191-24-2</t>
+          <t>207-08-9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BghiPe</t>
+          <t>BkF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>benzo(ghi)peryleen</t>
+          <t>benzo(k)fluorantheen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benzo (ghi) peryleen</t>
+          <t>Benzo (k) fluorantheen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>benzo(g,h,i)peryleen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BghiPe</t>
+          <t>BkF</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>benzo(g,h,i)peryleen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1087,32 +1087,32 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>42576-02-3</t>
+          <t>191-24-2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bfnx</t>
+          <t>BghiPe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bifenox</t>
+          <t>benzo(ghi)peryleen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>bifenox</t>
+          <t>Benzo (ghi) peryleen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1132,42 +1132,42 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>bifenox</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bfnx</t>
+          <t>BghiPe</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1135</v>
+        <v>1119</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>67-66-3</t>
+          <t>42576-02-3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TClC1a</t>
+          <t>bfnx</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>trichloormethaan (chloroform)</t>
+          <t>bifenox</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trichloormethaan</t>
+          <t>bifenox</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>trichloormethaan (chloroform)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TClC1a</t>
+          <t>bfnx</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1203,26 +1203,26 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>52315-07-8</t>
+          <t>67-66-3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cypmtn</t>
+          <t>TClC1a</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cypermethrin</t>
+          <t>trichloormethaan (chloroform)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>cypermetrine</t>
+          <t>Trichloormethaan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>cypermethrin</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cypmtn</t>
+          <t>TClC1a</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1258,26 +1258,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>72-54-8</t>
+          <t>52315-07-8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>44DDD</t>
+          <t>cypmtn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyldichloorethaan</t>
+          <t>cypermethrin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DDD pp'</t>
+          <t>cypermetrine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyldichloorethaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>44DDD</t>
+          <t>cypmtn</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1313,26 +1313,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>72-55-9</t>
+          <t>72-54-8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>44DDE</t>
+          <t>44DDD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyldichlooretheen</t>
+          <t>4,4'-dichloordifenyldichloorethaan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DDE pp'</t>
+          <t>DDD pp'</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyldichlooretheen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>44DDE</t>
+          <t>44DDD</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1368,26 +1368,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>789-02-6</t>
+          <t>72-55-9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24DDT</t>
+          <t>44DDE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2,4'-dichloordifenyltrichloorethaan</t>
+          <t>4,4'-dichloordifenyldichlooretheen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DDT op'</t>
+          <t>DDE pp'</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2,4'-dichloordifenyltrichloorethaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24DDT</t>
+          <t>44DDE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1423,26 +1423,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50-29-3</t>
+          <t>789-02-6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>44DDT</t>
+          <t>24DDT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyltrichloorethaan</t>
+          <t>2,4'-dichloordifenyltrichloorethaan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DDT pp'</t>
+          <t>DDT op'</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyltrichloorethaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>44DDT</t>
+          <t>24DDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1478,26 +1478,26 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>107-06-2</t>
+          <t>50-29-3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12DClC2a</t>
+          <t>44DDT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1,2-dichloorethaan</t>
+          <t>4,4'-dichloordifenyltrichloorethaan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1,2-dichloorethaan</t>
+          <t>DDT pp'</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1,2-dichloorethaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12DClC2a</t>
+          <t>44DDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1533,26 +1533,26 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>75-09-2</t>
+          <t>107-06-2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DClC1a</t>
+          <t>12DClC2a</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>dichloormethaan</t>
+          <t>1,2-dichloorethaan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dichloormethaan</t>
+          <t>1,2-dichloorethaan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>dichloormethaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>DClC1a</t>
+          <t>12DClC2a</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1588,26 +1588,26 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>62-73-7</t>
+          <t>75-09-2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DClvs</t>
+          <t>DClC1a</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dichloorvos</t>
+          <t>dichloormethaan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>dichloorvos</t>
+          <t>Dichloormethaan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>dichloorvos</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>DClvs</t>
+          <t>DClC1a</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1643,39 +1643,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>115-32-2</t>
+          <t>62-73-7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dcfl</t>
+          <t>DClvs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>dicofol</t>
+          <t>dichloorvos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dicofol</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+          <t>dichloorvos</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>dicofol</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Dcfl</t>
+          <t>DClvs</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1686,81 +1698,69 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>60-57-1</t>
+          <t>115-32-2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dieldn</t>
+          <t>Dcfl</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dieldrin</t>
+          <t>dicofol</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dieldrin</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Dicofol</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>dieldrin</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>dieldn</t>
+          <t>Dcfl</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>330-54-1</t>
+          <t>60-57-1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Durn</t>
+          <t>dieldn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>diuron</t>
+          <t>dieldrin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Diuron</t>
+          <t>Dieldrin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>diuron</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Durn</t>
+          <t>dieldn</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>diuron</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1851,26 +1851,26 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>959-98-8</t>
+          <t>330-54-1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>aedsfn</t>
+          <t>Durn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>alfa-endosulfan</t>
+          <t>diuron</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>alfa-Endosulfan</t>
+          <t>Diuron</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>alfa-endosulfan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>aedsfn</t>
+          <t>Durn</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1906,26 +1906,26 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33213-65-9</t>
+          <t>959-98-8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bedsfn</t>
+          <t>aedsfn</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>beta-endosulfan</t>
+          <t>alfa-endosulfan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>beta-Endosulfan</t>
+          <t>alfa-Endosulfan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>beta-endosulfan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>bedsfn</t>
+          <t>aedsfn</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1961,26 +1961,26 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>72-20-8</t>
+          <t>33213-65-9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>endn</t>
+          <t>bedsfn</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>endrin</t>
+          <t>beta-endosulfan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Endrin</t>
+          <t>beta-Endosulfan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>endrin</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>endn</t>
+          <t>bedsfn</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>endrin</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2071,26 +2071,26 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>206-44-0</t>
+          <t>72-20-8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Flu</t>
+          <t>endn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>fluorantheen</t>
+          <t>endrin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fluorantheen</t>
+          <t>Endrin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>fluorantheen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Flu</t>
+          <t>endn</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>fluorantheen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>76-44-8</t>
+          <t>206-44-0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HpCl</t>
+          <t>Flu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>heptachloor</t>
+          <t>fluorantheen</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>heptachloor</t>
+          <t>Fluorantheen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2220,42 +2220,42 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>heptachloor</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>HpCl</t>
+          <t>Flu</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1024-57-3</t>
+          <t>76-44-8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cHpClepO</t>
+          <t>HpCl</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cis-heptachloorepoxide</t>
+          <t>heptachloor</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>heptachloorepoxide</t>
+          <t>heptachloor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>cis-heptachloorepoxide</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>cHpClepO</t>
+          <t>HpCl</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>118-74-1</t>
+          <t>1024-57-3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>cHpClepO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>hexachloorbenzeen</t>
+          <t>cis-heptachloorepoxide</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hexachloorbenzeen</t>
+          <t>heptachloorepoxide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2330,42 +2330,42 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>hexachloorbenzeen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>cHpClepO</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>319-84-6</t>
+          <t>118-74-1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>aHCH</t>
+          <t>HCB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>alfa-hexachloorcyclohexaan</t>
+          <t>hexachloorbenzeen</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>alpha Hexachloorcyclohexaan</t>
+          <t>Hexachloorbenzeen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2385,42 +2385,42 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>alfa-hexachloorcyclohexaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>aHCH</t>
+          <t>HCB</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>319-85-7</t>
+          <t>319-84-6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bHCH</t>
+          <t>aHCH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>beta-hexachloorcyclohexaan</t>
+          <t>alfa-hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>beta Hexachloorcyclohexaan</t>
+          <t>alpha Hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>beta-hexachloorcyclohexaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>bHCH</t>
+          <t>aHCH</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2456,26 +2456,26 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>319-86-8</t>
+          <t>319-85-7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dHCH</t>
+          <t>bHCH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>delta-hexachloorcyclohexaan</t>
+          <t>beta-hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>delta Hexachloorcyclohexaan</t>
+          <t>beta Hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>delta-hexachloorcyclohexaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>dHCH</t>
+          <t>bHCH</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>delta-hexachloorcyclohexaan</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2566,26 +2566,26 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>58-89-9</t>
+          <t>319-86-8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>cHCH</t>
+          <t>dHCH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>gamma-hexachloorcyclohexaan (lindaan)</t>
+          <t>delta-hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>gamma Hexachloorcyclohexaan (Lindaan)</t>
+          <t>delta Hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>gamma-hexachloorcyclohexaan (lindaan)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>cHCH</t>
+          <t>dHCH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>gamma-hexachloorcyclohexaan (lindaan)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2676,26 +2676,26 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>193-39-5</t>
+          <t>58-89-9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>InP</t>
+          <t>cHCH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>indeno(1,2,3-cd)pyreen</t>
+          <t>gamma-hexachloorcyclohexaan (lindaan)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Indeno (123cd) pyreen</t>
+          <t>gamma Hexachloorcyclohexaan (Lindaan)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>indeno(1,2,3-c,d)pyreen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>InP</t>
+          <t>cHCH</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>indeno(1,2,3-c,d)pyreen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2780,32 +2780,32 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>465-73-6</t>
+          <t>193-39-5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>idn</t>
+          <t>InP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>isodrin</t>
+          <t>indeno(1,2,3-cd)pyreen</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Isodrin</t>
+          <t>Indeno (123cd) pyreen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2825,17 +2825,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>isodrin</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>idn</t>
+          <t>InP</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>isodrin</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2896,26 +2896,26 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>34123-59-6</t>
+          <t>465-73-6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>iptrn</t>
+          <t>idn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>isoproturon</t>
+          <t>isodrin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Isoproturon</t>
+          <t>Isodrin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>isoproturon</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>iptrn</t>
+          <t>idn</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>isoproturon</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3006,26 +3006,26 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1235</v>
+        <v>1208</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>87-86-5</t>
+          <t>34123-59-6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PeClFol</t>
+          <t>iptrn</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>pentachloorfenol</t>
+          <t>isoproturon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pentachloorfenol</t>
+          <t>Isoproturon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>pentachloorfenol</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PeClFol</t>
+          <t>iptrn</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3061,26 +3061,26 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1263</v>
+        <v>1235</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>122-34-9</t>
+          <t>87-86-5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>simzne</t>
+          <t>PeClFol</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>simazine</t>
+          <t>pentachloorfenol</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Simazine</t>
+          <t>Pentachloorfenol</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>simazine</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>simzne</t>
+          <t>PeClFol</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>simazine</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3171,26 +3171,26 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1272</v>
+        <v>1263</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>127-18-4</t>
+          <t>122-34-9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>T4ClC2e</t>
+          <t>simzne</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tetrachlooretheen (per)</t>
+          <t>simazine</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tetrachlooreth(yl)een</t>
+          <t>Simazine</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>tetrachlooretheen (per)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>T4ClC2e</t>
+          <t>simzne</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3226,26 +3226,26 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>56-23-5</t>
+          <t>886-50-0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>T4ClC1a</t>
+          <t>terbtn</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tetrachloormethaan (tetra)</t>
+          <t>terbutrin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tetrachloormethaan</t>
+          <t>Terbutryne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>tetrachloormethaan (tetra)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>T4ClC1a</t>
+          <t>terbtn</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3281,26 +3281,26 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1283</v>
+        <v>1272</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>120-82-1</t>
+          <t>127-18-4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>124TClBen</t>
+          <t>T4ClC2e</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1,2,4-trichloorbenzeen</t>
+          <t>tetrachlooretheen (per)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1,2,4 Trichloorbenzeen</t>
+          <t>Tetrachlooreth(yl)een</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1,2,4-trichloorbenzeen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>124TClBen</t>
+          <t>T4ClC2e</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3336,26 +3336,26 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1286</v>
+        <v>1276</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>79-01-6</t>
+          <t>56-23-5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TClC2e</t>
+          <t>T4ClC1a</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>trichlooretheen (tri)</t>
+          <t>tetrachloormethaan (tetra)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trichlooreth(yl)een</t>
+          <t>Tetrachloormethaan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>trichlooretheen (tri)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>TClC2e</t>
+          <t>T4ClC1a</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3391,26 +3391,26 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1582-09-8</t>
+          <t>120-82-1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tfrlne</t>
+          <t>124TClBen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>trifluraline</t>
+          <t>1,2,4-trichloorbenzeen</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trifluraline</t>
+          <t>1,2,4 Trichloorbenzeen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>trifluraline</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Tfrlne</t>
+          <t>124TClBen</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3446,26 +3446,26 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1337</v>
+        <v>1286</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16887-00-6</t>
+          <t>79-01-6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>TClC2e</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>chloride</t>
+          <t>trichlooretheen (tri)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chloride</t>
+          <t>Trichlooreth(yl)een</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3475,52 +3475,52 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>chloride</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>TClC2e</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1339</v>
+        <v>1289</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14797-65-0</t>
+          <t>1582-09-8</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NO2</t>
+          <t>Tfrlne</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>nitriet</t>
+          <t>trifluraline</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nitriet NO2</t>
+          <t>Trifluraline</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3530,52 +3530,52 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>nitriet</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>NO2</t>
+          <t>Tfrlne</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Nnf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14797-65-0</t>
+          <t>16887-00-6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NO2</t>
+          <t>Cl</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>nitriet</t>
+          <t>chloride</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nitriet NO2</t>
+          <t>Chloride</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3585,57 +3585,57 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>nitriet</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>NO2</t>
+          <t>Cl</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Nnf</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1369</v>
+        <v>1339</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>14797-65-0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>NO2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>nitriet</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Arseen  opgelost</t>
+          <t>Nitriet NO2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3645,77 +3645,77 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>mg/L N</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>NO2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>Nnf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1369</v>
+        <v>1339</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>14797-65-0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>NO2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>nitriet</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arseen  opgelost</t>
+          <t>Nitriet NO2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>mg/L N</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>NO2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>Nnf</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3825,13 +3825,13 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1379</v>
+        <v>1369</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>kobalt opgelost</t>
+          <t>Arseen  opgelost</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3880,13 +3880,13 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1379</v>
+        <v>1369</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>kobalt opgelost</t>
+          <t>Arseen  opgelost</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3935,32 +3935,32 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7439-92-1</t>
+          <t>7440-38-2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>As</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>arseen</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lood (Pb) opgelost</t>
+          <t>kobalt opgelost</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3980,42 +3980,42 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>As</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7439-92-1</t>
+          <t>7440-38-2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>As</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>arseen</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lood (Pb) opgelost</t>
+          <t>kobalt opgelost</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>As</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4155,32 +4155,32 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7440-02-0</t>
+          <t>7439-92-1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>lood</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nikkel (Ni) opgelost</t>
+          <t>Lood (Pb) opgelost</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4200,42 +4200,42 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7440-02-0</t>
+          <t>7439-92-1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>lood</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nikkel (Ni) opgelost</t>
+          <t>Lood (Pb) opgelost</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4375,32 +4375,32 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7439-97-6</t>
+          <t>7440-02-0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hg</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>kwik</t>
+          <t>nikkel</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kwik (Hg) opgelost</t>
+          <t>Nikkel (Ni) opgelost</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4420,42 +4420,42 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>kwik</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Hg</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7439-97-6</t>
+          <t>7440-02-0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hg</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>kwik</t>
+          <t>nikkel</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kwik (Hg) opgelost</t>
+          <t>Nikkel (Ni) opgelost</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4475,47 +4475,47 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>kwik</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Hg</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>7439-97-6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>kwik</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
+          <t>Kwik (Hg) opgelost</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4546,31 +4546,31 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>7439-97-6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>kwik</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
+          <t>Kwik (Hg) opgelost</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -4680,32 +4680,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>CONCTTE</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>nf</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>cadmium</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -4735,12 +4735,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -4790,12 +4790,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4815,42 +4815,42 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7440-50-8</t>
+          <t>7440-43-9</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>cadmium</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>koper (Cu) opgelost</t>
+          <t>Cadmium (Cd) opgelost</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4860,72 +4860,72 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7440-50-8</t>
+          <t>7440-43-9</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>cadmium</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>koper (Cu) opgelost</t>
+          <t>Cadmium (Cd) opgelost</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>CONCTTE</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>nf</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>koper</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5035,32 +5035,32 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1433</v>
+        <v>1392</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>14265-44-2</t>
+          <t>7440-50-8</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PO4</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>fosfaat</t>
+          <t>koper</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Opgeloste orthofosfaten</t>
+          <t>koper (Cu) opgelost</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5075,52 +5075,52 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>mg/L P</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>orthofosfaat</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>PO4</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Pnf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1439</v>
+        <v>1392</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>479-61-8</t>
+          <t>7440-50-8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CHLFa</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>chlorofyl-a</t>
+          <t>koper</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chlorofyl a</t>
+          <t>koper (Cu) opgelost</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5135,97 +5135,97 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>chlorofyl-a</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>CHLFa</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>479-61-8</t>
+          <t>14265-44-2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CHLFa</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>chlorofyl-a</t>
+          <t>fosfaat</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chlorofyl a</t>
+          <t>Opgeloste orthofosfaten</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>mg/L P</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>chlorofyl-a</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>CHLFa</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>Pnf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1458</v>
+        <v>1439</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>120-12-7</t>
+          <t>479-61-8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>CHLFa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>antraceen</t>
+          <t>chlorofyl-a</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Antraceen</t>
+          <t>Chlorofyl a</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>antraceen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>CHLFa</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5261,26 +5261,26 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1458</v>
+        <v>1439</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>120-12-7</t>
+          <t>479-61-8</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>CHLFa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>antraceen</t>
+          <t>chlorofyl-a</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Antraceen</t>
+          <t>Chlorofyl a</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>antraceen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>CHLFa</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5316,26 +5316,26 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>470-90-6</t>
+          <t>120-12-7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Clfvfs</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>chloorfenvinfos</t>
+          <t>antraceen</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chloorfenvinfos</t>
+          <t>Antraceen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5355,42 +5355,42 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>chloorfenvinfos</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Clfvfs</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1517</v>
+        <v>1458</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>91-20-3</t>
+          <t>120-12-7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Naf</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>naftaleen</t>
+          <t>antraceen</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Naftaleen</t>
+          <t>Antraceen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5410,42 +5410,42 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>naftaleen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Naf</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1517</v>
+        <v>1464</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>91-20-3</t>
+          <t>470-90-6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Naf</t>
+          <t>Clfvfs</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>naftaleen</t>
+          <t>chloorfenvinfos</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Naftaleen</t>
+          <t>Chloorfenvinfos</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>naftaleen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Naf</t>
+          <t>Clfvfs</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5481,26 +5481,26 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1629</v>
+        <v>1517</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>108-70-3</t>
+          <t>91-20-3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>135TClBen</t>
+          <t>Naf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1,3,5-trichloorbenzeen</t>
+          <t>naftaleen</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1,3,5 Trichloorbenzeen</t>
+          <t>Naftaleen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1,3,5-trichloorbenzeen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>135TClBen</t>
+          <t>Naf</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5536,26 +5536,26 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1630</v>
+        <v>1517</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>87-61-6</t>
+          <t>91-20-3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>123TClBen</t>
+          <t>Naf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1,2,3-trichloorbenzeen</t>
+          <t>naftaleen</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1,2,3 Trichloorbenzeen</t>
+          <t>Naftaleen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1,2,3-trichloorbenzeen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>123TClBen</t>
+          <t>Naf</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5591,26 +5591,26 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1652</v>
+        <v>1629</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>87-68-3</t>
+          <t>108-70-3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HxClbtDen</t>
+          <t>135TClBen</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>hexachloorbutadieen</t>
+          <t>1,3,5-trichloorbenzeen</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hexachloorbutadieen</t>
+          <t>1,3,5 Trichloorbenzeen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>hexachloorbutadieen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>HxClbtDen</t>
+          <t>135TClBen</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5646,26 +5646,26 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1688</v>
+        <v>1630</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>74070-46-5</t>
+          <t>87-61-6</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>acnfn</t>
+          <t>123TClBen</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>aclonifen</t>
+          <t>1,2,3-trichloorbenzeen</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>aclonifen</t>
+          <t>1,2,3 Trichloorbenzeen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>aclonifen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>acnfn</t>
+          <t>123TClBen</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5701,26 +5701,26 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1688</v>
+        <v>1652</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>74070-46-5</t>
+          <t>87-68-3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>acnfn</t>
+          <t>HxClbtDen</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>aclonifen</t>
+          <t>hexachloorbutadieen</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>aclonifen</t>
+          <t>Hexachloorbutadieen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5740,42 +5740,42 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>aclonifen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>acnfn</t>
+          <t>HxClbtDen</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1877</v>
+        <v>1688</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>138261-41-3</t>
+          <t>74070-46-5</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>imdcpd</t>
+          <t>acnfn</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>imidacloprid</t>
+          <t>aclonifen</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>imidacloprid</t>
+          <t>aclonifen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>imidacloprid</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>imdcpd</t>
+          <t>acnfn</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5811,26 +5811,26 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1877</v>
+        <v>1688</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>138261-41-3</t>
+          <t>74070-46-5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>imdcpd</t>
+          <t>acnfn</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>imidacloprid</t>
+          <t>aclonifen</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>imidacloprid</t>
+          <t>aclonifen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>imidacloprid</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>imdcpd</t>
+          <t>acnfn</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5866,26 +5866,26 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1888</v>
+        <v>1877</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>608-93-5</t>
+          <t>138261-41-3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PeClBen</t>
+          <t>imdcpd</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>pentachloorbenzeen</t>
+          <t>imidacloprid</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pentachloorbenzeen</t>
+          <t>imidacloprid</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>pentachloorbenzeen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>PeClBen</t>
+          <t>imdcpd</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5921,26 +5921,26 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1935</v>
+        <v>1877</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>28159-98-0</t>
+          <t>138261-41-3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>irgrl</t>
+          <t>imdcpd</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>irgarol</t>
+          <t>imidacloprid</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>cybutryne</t>
+          <t>imidacloprid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>irgarol</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>irgrl</t>
+          <t>imdcpd</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5976,26 +5976,26 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1959</v>
+        <v>1888</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>140-66-9</t>
+          <t>608-93-5</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4ttC8yFol</t>
+          <t>PeClBen</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4-tertiair-octylfenol</t>
+          <t>pentachloorbenzeen</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4-(1,1',3,3' - tetramethylbutyl)-fenol (Para-tert-octylfenol)</t>
+          <t>Pentachloorbenzeen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4-tertiair-octylfenol</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>4ttC8yFol</t>
+          <t>PeClBen</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6031,26 +6031,26 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2028</v>
+        <v>1935</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>124495-18-7</t>
+          <t>28159-98-0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>quinoxfn</t>
+          <t>irgrl</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>quinoxyfen</t>
+          <t>irgarol</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Quinoxyfen</t>
+          <t>cybutryne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>quinoxyfen</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>quinoxfn</t>
+          <t>irgrl</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6086,26 +6086,26 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2879</v>
+        <v>1959</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>36643-28-4</t>
+          <t>140-66-9</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TC4ySn</t>
+          <t>4ttC8yFol</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>tributyltin (kation)</t>
+          <t>4-tertiair-octylfenol</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Verbindingen van tributyltin (Tributyltin kation)</t>
+          <t>4-(1,1',3,3' - tetramethylbutyl)-fenol (Para-tert-octylfenol)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>tributyltin (kation)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>TC4ySn</t>
+          <t>4ttC8yFol</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6141,26 +6141,26 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2879</v>
+        <v>2028</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>36643-28-4</t>
+          <t>124495-18-7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TC4ySn</t>
+          <t>quinoxfn</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>tributyltin (kation)</t>
+          <t>quinoxyfen</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Verbindingen van tributyltin (Tributyltin kation)</t>
+          <t>Quinoxyfen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>tributyltin (kation)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>TC4ySn</t>
+          <t>quinoxfn</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6196,39 +6196,51 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2911</v>
+        <v>2879</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>207122-15-4</t>
+          <t>36643-28-4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PBDE154</t>
+          <t>TC4ySn</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2,2',4,4',5,6'-hexabroomdifenylether</t>
+          <t>tributyltin (kation)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PBDE154 (2,2',4,4',5,6'-hexabroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+          <t>Verbindingen van tributyltin (Tributyltin kation)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2,2',4,4',5,6'-hexabroomdifenylether</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>PBDE154</t>
+          <t>TC4ySn</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6239,39 +6251,51 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2912</v>
+        <v>2879</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>68631-49-2</t>
+          <t>36643-28-4</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PBDE153</t>
+          <t>TC4ySn</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2,2',4,4',5,5'-hexabroomdifenylether</t>
+          <t>tributyltin (kation)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PBDE153 (2,2',4,4',5,5'-hexabroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+          <t>Verbindingen van tributyltin (Tributyltin kation)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2,2',4,4',5,5'-hexabroomdifenylether</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>PBDE153</t>
+          <t>TC4ySn</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6282,26 +6306,26 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2915</v>
+        <v>2911</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>189084-64-8</t>
+          <t>207122-15-4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PBDE100</t>
+          <t>PBDE154</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2,2',4,4',6-pentabroomdifenylether</t>
+          <t>2,2',4,4',5,6'-hexabroomdifenylether</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PBDE100 (2,2',4,4',6-pentabroomdifenylether)</t>
+          <t>PBDE154 (2,2',4,4',5,6'-hexabroomdifenylether)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -6309,12 +6333,12 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2,2',4,4',6-pentabroomdifenylether</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>PBDE100</t>
+          <t>PBDE154</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6325,26 +6349,26 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2916</v>
+        <v>2912</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>60348-60-9</t>
+          <t>68631-49-2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PBDE99</t>
+          <t>PBDE153</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2,2',4,4',5-pentabroomdifenylether</t>
+          <t>2,2',4,4',5,5'-hexabroomdifenylether</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PBDE99 (2,2',4,4',5-pentabroomdifenylether)</t>
+          <t>PBDE153 (2,2',4,4',5,5'-hexabroomdifenylether)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -6352,42 +6376,42 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2,2',4,4',5-pentabroomdifenylether</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>PBDE99</t>
+          <t>PBDE153</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2919</v>
+        <v>2915</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5436-43-1</t>
+          <t>189084-64-8</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PBDE47</t>
+          <t>PBDE100</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2,2',4,4'-tetrabroomdifenylether</t>
+          <t>2,2',4,4',6-pentabroomdifenylether</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PBDE47 (2,2',4,4'-tetrabroomdifenylether)</t>
+          <t>PBDE100 (2,2',4,4',6-pentabroomdifenylether)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -6395,42 +6419,42 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2,2',4,4'-tetrabroomdifenylether</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>PBDE47</t>
+          <t>PBDE100</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2920</v>
+        <v>2916</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>41318-75-6</t>
+          <t>60348-60-9</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PBDE28</t>
+          <t>PBDE99</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2,4,4'-tribroomdifenylether</t>
+          <t>2,2',4,4',5-pentabroomdifenylether</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PBDE28 (2,4,4'-tribroomdifenylether)</t>
+          <t>PBDE99 (2,2',4,4',5-pentabroomdifenylether)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -6438,152 +6462,128 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2,4,4'-tribroomdifenylether</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>PBDE28</t>
+          <t>PBDE99</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>5347</v>
+        <v>2919</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>335-67-1</t>
+          <t>5436-43-1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PFOA</t>
+          <t>PBDE47</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>perfluoroctaanzuur</t>
+          <t>2,2',4,4'-tetrabroomdifenylether</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>PBDE47 (2,2',4,4'-tetrabroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>perfluoroctaanzuur</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>PFOA</t>
+          <t>PBDE47</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>5347</v>
+        <v>2920</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>335-67-1</t>
+          <t>41318-75-6</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PFOA</t>
+          <t>PBDE28</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>perfluoroctaanzuur</t>
+          <t>2,4,4'-tribroomdifenylether</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>PBDE28 (2,4,4'-tribroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>perfluoroctaanzuur</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>PFOA</t>
+          <t>PBDE28</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>5978</v>
+        <v>5347</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>307-24-4</t>
+          <t>335-67-1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PFHxA</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>perfluorhexaanzuur</t>
+          <t>perfluoroctaanzuur</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PFHxA</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>perfluor-n-hexaanzuur</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>PFHxA</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>5978</v>
+        <v>5347</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>307-24-4</t>
+          <t>335-67-1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PFHxA</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>perfluorhexaanzuur</t>
+          <t>perfluoroctaanzuur</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PFHxA</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6658,42 +6658,42 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>perfluor-n-hexaanzuur</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>PFHxA</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5979</v>
+        <v>5978</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2706-90-3</t>
+          <t>307-24-4</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PFPA</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>perfluorpentaanzuur</t>
+          <t>perfluorhexaanzuur</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PFPeA</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6713,42 +6713,42 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>perfluor-n-pentaanzuur</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>PFPA</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5979</v>
+        <v>5978</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2706-90-3</t>
+          <t>307-24-4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PFPA</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>perfluorpentaanzuur</t>
+          <t>perfluorhexaanzuur</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PFPeA</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6768,42 +6768,42 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>perfluor-n-pentaanzuur</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>PFPA</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>6616</v>
+        <v>5979</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>117-81-7</t>
+          <t>2706-90-3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DEHP</t>
+          <t>PFPA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
+          <t>perfluorpentaanzuur</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Di(2-ethylhexyl)ftalaat DEHP</t>
+          <t>PFPeA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6823,42 +6823,42 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>DEHP</t>
+          <t>PFPA</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>6616</v>
+        <v>5979</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>117-81-7</t>
+          <t>2706-90-3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DEHP</t>
+          <t>PFPA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
+          <t>perfluorpentaanzuur</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Di(2-ethylhexyl)ftalaat DEHP</t>
+          <t>PFPeA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6878,42 +6878,42 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>DEHP</t>
+          <t>PFPA</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6830</v>
+        <v>6616</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>355-46-4</t>
+          <t>117-81-7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>L_PFHxS</t>
+          <t>DEHP</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>perfluorhexaansulfonzuur</t>
+          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PFHxS</t>
+          <t>Di(2-ethylhexyl)ftalaat DEHP</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>perfluor-1-hexaansulfonaat (lineair)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>L_PFHxS</t>
+          <t>DEHP</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -6949,26 +6949,26 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>6830</v>
+        <v>6616</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>355-46-4</t>
+          <t>117-81-7</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>L_PFHxS</t>
+          <t>DEHP</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>perfluorhexaansulfonzuur</t>
+          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PFHxS</t>
+          <t>Di(2-ethylhexyl)ftalaat DEHP</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>perfluor-1-hexaansulfonaat (lineair)</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>L_PFHxS</t>
+          <t>DEHP</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7004,109 +7004,219 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>7073</v>
+        <v>6830</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16984-48-8</t>
+          <t>355-46-4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L_PFHxS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>fluoride</t>
+          <t>perfluorhexaansulfonzuur</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Anorganische fluoriden = fluoride opgelost</t>
+          <t>PFHxS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>fluoride</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L_PFHxS</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
+        <v>6830</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>355-46-4</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>L_PFHxS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>perfluorhexaansulfonzuur</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>PFHxS</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>CONCTTE</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>L_PFHxS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>OPGLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
         <v>7073</v>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>16984-48-8</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>fluoride</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Anorganische fluoriden = fluoride opgelost</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>nf</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>CONCTTE</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>7073</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>16984-48-8</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>fluoride</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Anorganische fluoriden = fluoride opgelost</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>nf</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>CONCTTE</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -7123,7 +7233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7169,17 +7279,17 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>DONAR_Parameter</t>
+          <t>grootheid_code</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>DONAR_PARCode</t>
+          <t>wadar_PARCode</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>HDH</t>
+          <t>hoedanigheid_code</t>
         </is>
       </c>
     </row>
@@ -7247,26 +7357,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1083</v>
+        <v>1116</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2921-88-2</t>
+          <t>205-99-2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C2yClprfs</t>
+          <t>BbF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ethylchloorpyrifos</t>
+          <t>benzo(b)fluorantheen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chloorpyrifos (Chloorpyrifos ethyl)</t>
+          <t>Benzo (b) fluorantheen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7276,7 +7386,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7319,7 +7429,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7333,26 +7443,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1116</v>
+        <v>1143</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>205-99-2</t>
+          <t>53-19-0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BbF</t>
+          <t>24DDD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>benzo(b)fluorantheen</t>
+          <t>2,4'-dichloordifenyldichloorethaan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Benzo (b) fluorantheen</t>
+          <t>DDD op'</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7376,26 +7486,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53-19-0</t>
+          <t>3424-82-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>24DDD</t>
+          <t>24DDE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2,4'-dichloordifenyldichloorethaan</t>
+          <t>2,4'-dichloordifenyldichlooretheen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DDD op'</t>
+          <t>DDE op'</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7419,26 +7529,18 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1145</v>
+        <v>1301</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3424-82-6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>24DDE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2,4'-dichloordifenyldichlooretheen</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DDE op'</t>
+          <t>Watertemperatuur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7448,12 +7550,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -7462,26 +7564,18 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1269</v>
+        <v>1302</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>886-50-0</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>terbtn</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>terbutrin</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terbutryne</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7491,12 +7585,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>u pH</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -7505,7 +7599,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -7516,7 +7610,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Watertemperatuur</t>
+          <t>Geleidbaarheid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7531,7 +7625,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>µS/cm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -7540,7 +7634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -7551,7 +7645,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Zwevende stoffen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7566,7 +7660,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>u pH</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -7575,7 +7669,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -7586,7 +7680,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Geleidbaarheid</t>
+          <t>Zwevende stoffen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7596,12 +7690,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>µS/cm</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -7610,123 +7704,123 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80937-33-3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zwevende stoffen</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
+          <t>Opgeloste zuurstof</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80937-33-3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zwevende stoffen</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
+          <t>Opgeloste zuurstof</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>80937-33-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opgeloste zuurstof</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+          <t>BZV5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mgO2/L</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>80937-33-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opgeloste zuurstof</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+          <t>BZV5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>mgO2/L</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -7737,7 +7831,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BZV5</t>
+          <t>CZV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -7747,7 +7841,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7761,7 +7855,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -7772,7 +7866,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BZV5</t>
+          <t>CZV</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -7782,7 +7876,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7796,7 +7890,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -7807,7 +7901,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CZV</t>
+          <t>Kjeldahl stikstof</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -7822,7 +7916,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>mgO2/L</t>
+          <t>mg/L N</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7831,7 +7925,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -7842,7 +7936,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CZV</t>
+          <t>Kjeldahl stikstof</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7857,7 +7951,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>mgO2/L</t>
+          <t>mg/L N</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7866,18 +7960,18 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1319</v>
+        <v>1335</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6684-80-6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kjeldahl stikstof</t>
+          <t>Ammonium NH4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7901,18 +7995,18 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1319</v>
+        <v>1335</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6684-80-6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kjeldahl stikstof</t>
+          <t>Ammonium NH4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -7936,18 +8030,18 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6684-80-6</t>
+          <t>18785-72-3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ammonium NH4</t>
+          <t>Sulfaat</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7962,7 +8056,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -7971,18 +8065,18 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6684-80-6</t>
+          <t>84145-82-4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ammonium NH4</t>
+          <t>Nitraat NO3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7992,7 +8086,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8006,18 +8100,18 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18785-72-3</t>
+          <t>84145-82-4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sulfaat</t>
+          <t>Nitraat NO3</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8027,12 +8121,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>mg/L N</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -8041,18 +8135,18 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>84145-82-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nitraat NO3</t>
+          <t>Hardheid TH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8067,7 +8161,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>°F</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -8076,18 +8170,18 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>84145-82-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nitraat NO3</t>
+          <t>Totaal fosfor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8097,12 +8191,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>mg/L P</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -8111,23 +8205,19 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1345</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>1361</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hardheid TH</t>
+          <t>Uraan (U) opgelost</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8137,7 +8227,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>°F</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -8146,33 +8236,29 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1350</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>1361</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Totaal fosfor</t>
+          <t>Uraan (U) opgelost</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>mg/L P</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -8181,14 +8267,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Uraan (U) opgelost</t>
+          <t>Zilver (Ag) opgelost</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8198,7 +8284,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8212,14 +8298,18 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1361</v>
-      </c>
-      <c r="B31" t="inlineStr"/>
+        <v>1383</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>9029-97-4</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Uraan (U) opgelost</t>
+          <t>Zink (Zn) opgelost</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -8243,14 +8333,18 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1368</v>
-      </c>
-      <c r="B32" t="inlineStr"/>
+        <v>1383</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>9029-97-4</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zilver (Ag) opgelost</t>
+          <t>Zink (Zn) opgelost</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -8260,7 +8354,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -8274,18 +8368,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1383</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>9029-97-4</t>
-        </is>
-      </c>
+        <v>1385</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zink (Zn) opgelost</t>
+          <t>Seleen (Se) opgelost</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -8309,18 +8399,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1383</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>9029-97-4</t>
-        </is>
-      </c>
+        <v>1385</v>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zink (Zn) opgelost</t>
+          <t>Seleen (Se) opgelost</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -8344,29 +8430,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1385</v>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+        <v>1551</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7727-37-9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>distikstof</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Seleen (Se) opgelost</t>
+          <t>Totaal stikstof (Kj + NO2 + NO3)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>mg/L N</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8375,24 +8473,36 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1385</v>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+        <v>1743</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>115-29-7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>endsfn</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>endosulfan (som alfa- en beta-isomeer)</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Seleen (Se) opgelost</t>
+          <t>Endosulfan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -8406,26 +8516,26 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1551</v>
+        <v>1774</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7727-37-9</t>
+          <t>12002-48-1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>TClBen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>distikstof</t>
+          <t>trichloorbenzeen</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Totaal stikstof (Kj + NO2 + NO3)</t>
+          <t>Trichloorbenzenen (alle isomeren)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8435,12 +8545,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -8449,112 +8559,88 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1743</v>
+        <v>1920</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>115-29-7</t>
+          <t>1806-26-4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>endsfn</t>
+          <t>4C8yFol</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>endosulfan (som alfa- en beta-isomeer)</t>
+          <t>4-n-octylfenol</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Endosulfan</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Octylfenolen</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1774</v>
+        <v>1955</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12002-48-1</t>
+          <t>85535-84-8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TClBen</t>
+          <t>sC10C13Clakn</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>trichloorbenzeen</t>
+          <t>som C10-C13-chlooralkanen</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trichloorbenzenen (alle isomeren)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>C10-C13-chlooralkanen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1920</v>
+        <v>1958</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1806-26-4</t>
+          <t>104-40-5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4C8yFol</t>
+          <t>4C9yFol</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4-n-octylfenol</t>
+          <t>4-nonylfenol</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Octylfenolen</t>
+          <t>4-nonylfenol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -8566,26 +8652,26 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1955</v>
+        <v>5474</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>85535-84-8</t>
+          <t>25154-52-3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sC10C13Clakn</t>
+          <t>C9yFol</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>som C10-C13-chlooralkanen</t>
+          <t>nonylfenol</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>C10-C13-chlooralkanen</t>
+          <t>Nonylfenolen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -8597,80 +8683,92 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1958</v>
+        <v>5534</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>104-40-5</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>4C9yFol</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>4-nonylfenol</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4-nonylfenol</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+          <t>Som aldrin+endrin+dieldrin+isodrin</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5474</v>
+        <v>5537</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>25154-52-3</t>
+          <t>608-73-1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C9yFol</t>
+          <t>sHCH</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>nonylfenol</t>
+          <t>som hexachloorcyclohexaan-isomeren</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nonylfenolen</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+          <t>Hexachloorcyclohexaan</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5534</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>5977</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Som aldrin+endrin+dieldrin+isodrin</t>
+          <t xml:space="preserve"> PFHpA </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8694,26 +8792,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>5537</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>608-73-1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>sHCH</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>som hexachloorcyclohexaan-isomeren</t>
-        </is>
-      </c>
+        <v>5977</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hexachloorcyclohexaan</t>
+          <t xml:space="preserve"> PFHpA </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8723,7 +8809,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -8737,14 +8823,26 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5977</v>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+        <v>6561</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1763-23-1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PFOS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>perfluoroctaansulfonzuur</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PFHpA </t>
+          <t>Perfluor octaanzuur PFOS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8768,14 +8866,26 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5977</v>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+        <v>6561</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1763-23-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PFOS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>perfluoroctaansulfonzuur</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PFHpA </t>
+          <t>Perfluor octaanzuur PFOS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8799,104 +8909,72 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6561</v>
+        <v>6678</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1763-23-1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>PFOS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>perfluoroctaansulfonzuur</t>
-        </is>
-      </c>
+          <t>32534-81-9</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Perfluor octaanzuur PFOS</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Pentabroomdifenylether som</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6561</v>
+        <v>6678</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1763-23-1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>PFOS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>perfluoroctaansulfonzuur</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Perfluor octaanzuur PFOS</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>polybroomdifenylether, totaal</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6678</v>
+        <v>7128</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>32534-81-9</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>3194-55-6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sHBCD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>som 1,2,5,6,9,10-hexabroomcyclododecaan</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pentabroomdifenylether som</t>
+          <t>hexabroom-cyclododecaan (HBCDD)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -8908,83 +8986,101 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6678</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>7170</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>polybroomdifenylether, totaal</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+          <t xml:space="preserve">Som DDT 2,4' &amp; 4,4', DDD 2,4' &amp; 4,4'  DDE 2,4' &amp; 4,4' </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>7128</v>
+        <v>7706</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3194-55-6</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>sHBCD</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>som 1,2,5,6,9,10-hexabroomcyclododecaan</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>hexabroom-cyclododecaan (HBCDD)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+          <t>Heptachloor + heptachloorepoxide</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>7170</v>
-      </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Som DDT 2,4' &amp; 4,4', DDD 2,4' &amp; 4,4'  DDE 2,4' &amp; 4,4' </t>
+          <t>Opgeloste organische koolstof DOC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>=</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8992,8 +9088,10 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>7706</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COT</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -9004,24 +9102,12 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heptachloor + heptachloorepoxide</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Totaal organische koolstof TOC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -9029,36 +9115,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>DIAT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EEA_124-04-9 *</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Opgeloste organische koolstof DOC</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
+          <t>Evaluatie biologische kwaliteit - Diatomeeën</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -9066,19 +9140,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COT</t>
+          <t>FISH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EEA_14-02-8 *</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Totaal organische koolstof TOC</t>
+          <t>Evaluatie biologische kwaliteit -Vis</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -9091,21 +9165,13 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DIAT</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>EEA_124-04-9 *</t>
-        </is>
-      </c>
+          <t>IBGA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Evaluatie biologische kwaliteit - Diatomeeën</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -9116,21 +9182,13 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FISH</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>EEA_14-02-8 *</t>
-        </is>
-      </c>
+          <t>IBGN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Evaluatie biologische kwaliteit -Vis</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -9141,13 +9199,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IBGA</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>INV</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EEA_13-01-4 *</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Evaluatie biologische kwaliteit - Macro-invertebraten</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -9158,13 +9224,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IBGN</t>
+          <t>Unieke identificatie gemeten parameter
+Sandre code</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PARAMETER</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -9173,21 +9244,17 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>INV</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EEA_13-01-4 *</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Evaluatie biologische kwaliteit - Macro-invertebraten</t>
+          <t>Dioxines en verbindingen van het dioxinetype</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -9198,20 +9265,11 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Unieke identificatie gemeten parameter
-Sandre code</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>PARAMETER</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
@@ -9219,40 +9277,6 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Dioxines en verbindingen van het dioxinetype</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mappings/parameter_e_h_g.xlsx
+++ b/mappings/parameter_e_h_g.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,25 +462,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Aanpak kwantificeringsgrens</t>
+          <t>Unieke identificatie van de eenheid</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Unieke identificatie van de eenheid</t>
+          <t>grootheid_code</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>grootheid_code</t>
+          <t>wadar_PARCode</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>wadar_PARCode</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hoedanigheid_code</t>
         </is>
@@ -517,25 +512,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>C2yClprfs</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>C2yClprfs</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -572,25 +562,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>alCl</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>alCl</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -627,25 +612,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>aldn</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
-        <is>
-          <t>aldn</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -682,25 +662,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>atzne</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
-        <is>
-          <t>atzne</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -708,26 +683,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1912-24-9</t>
+          <t>71-43-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>atzne</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>atrazine</t>
+          <t>benzeen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atrazine</t>
+          <t>Benzeen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -737,25 +712,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
-        <is>
-          <t>atzne</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -763,26 +733,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71-43-2</t>
+          <t>50-32-8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>BaP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>benzeen</t>
+          <t>benzo(a)pyreen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Benzeen</t>
+          <t>Benzo (a) pyreen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -792,52 +762,47 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>BaP</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ben</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50-32-8</t>
+          <t>207-08-9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BaP</t>
+          <t>BkF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>benzo(a)pyreen</t>
+          <t>benzo(k)fluorantheen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Benzo (a) pyreen</t>
+          <t>Benzo (k) fluorantheen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -847,25 +812,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>BkF</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
-        <is>
-          <t>BaP</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>OPGLT</t>
         </is>
@@ -873,26 +833,26 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50-32-8</t>
+          <t>191-24-2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BaP</t>
+          <t>BghiPe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>benzo(a)pyreen</t>
+          <t>benzo(ghi)peryleen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Benzo (a) pyreen</t>
+          <t>Benzo (ghi) peryleen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -902,25 +862,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>BghiPe</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
-        <is>
-          <t>BaP</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
         <is>
           <t>OPGLT</t>
         </is>
@@ -928,26 +883,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>207-08-9</t>
+          <t>42576-02-3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BkF</t>
+          <t>bfnx</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>benzo(k)fluorantheen</t>
+          <t>bifenox</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Benzo (k) fluorantheen</t>
+          <t>bifenox</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -957,52 +912,47 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>bfnx</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>BkF</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1117</v>
+        <v>1135</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>207-08-9</t>
+          <t>67-66-3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BkF</t>
+          <t>TClC1a</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>benzo(k)fluorantheen</t>
+          <t>trichloormethaan (chloroform)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benzo (k) fluorantheen</t>
+          <t>Trichloormethaan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1012,52 +962,47 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>TClC1a</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BkF</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1118</v>
+        <v>1140</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>191-24-2</t>
+          <t>52315-07-8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BghiPe</t>
+          <t>cypmtn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>benzo(ghi)peryleen</t>
+          <t>cypermethrin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benzo (ghi) peryleen</t>
+          <t>cypermetrine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1067,52 +1012,47 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>cypmtn</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BghiPe</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>191-24-2</t>
+          <t>72-54-8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BghiPe</t>
+          <t>44DDD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>benzo(ghi)peryleen</t>
+          <t>4,4'-dichloordifenyldichloorethaan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benzo (ghi) peryleen</t>
+          <t>DDD pp'</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1122,52 +1062,47 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>44DDD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BghiPe</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1119</v>
+        <v>1146</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>42576-02-3</t>
+          <t>72-55-9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bfnx</t>
+          <t>44DDE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>bifenox</t>
+          <t>4,4'-dichloordifenyldichlooretheen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>bifenox</t>
+          <t>DDE pp'</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1177,25 +1112,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>44DDE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
-        <is>
-          <t>bfnx</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1203,26 +1133,26 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>67-66-3</t>
+          <t>789-02-6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TClC1a</t>
+          <t>24DDT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>trichloormethaan (chloroform)</t>
+          <t>2,4'-dichloordifenyltrichloorethaan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trichloormethaan</t>
+          <t>DDT op'</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1232,25 +1162,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>24DDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
-        <is>
-          <t>TClC1a</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1258,26 +1183,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52315-07-8</t>
+          <t>50-29-3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cypmtn</t>
+          <t>44DDT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cypermethrin</t>
+          <t>4,4'-dichloordifenyltrichloorethaan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>cypermetrine</t>
+          <t>DDT pp'</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1287,25 +1212,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>44DDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
-        <is>
-          <t>cypmtn</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1313,26 +1233,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1144</v>
+        <v>1161</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>72-54-8</t>
+          <t>107-06-2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>44DDD</t>
+          <t>12DClC2a</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyldichloorethaan</t>
+          <t>1,2-dichloorethaan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DDD pp'</t>
+          <t>1,2-dichloorethaan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1342,25 +1262,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>12DClC2a</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
-        <is>
-          <t>44DDD</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1368,26 +1283,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1146</v>
+        <v>1168</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>72-55-9</t>
+          <t>75-09-2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>44DDE</t>
+          <t>DClC1a</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyldichlooretheen</t>
+          <t>dichloormethaan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DDE pp'</t>
+          <t>Dichloormethaan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1397,25 +1312,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>DClC1a</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
-        <is>
-          <t>44DDE</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1423,26 +1333,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1147</v>
+        <v>1170</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>789-02-6</t>
+          <t>62-73-7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>24DDT</t>
+          <t>DClvs</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2,4'-dichloordifenyltrichloorethaan</t>
+          <t>dichloorvos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DDT op'</t>
+          <t>dichloorvos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1452,25 +1362,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>DClvs</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
-        <is>
-          <t>24DDT</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1478,81 +1383,68 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1148</v>
+        <v>1172</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50-29-3</t>
+          <t>115-32-2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>44DDT</t>
+          <t>Dcfl</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4,4'-dichloordifenyltrichloorethaan</t>
+          <t>dicofol</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DDT pp'</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Dicofol</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Dcfl</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>44DDT</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1161</v>
+        <v>1173</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>107-06-2</t>
+          <t>60-57-1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12DClC2a</t>
+          <t>dieldn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1,2-dichloorethaan</t>
+          <t>dieldrin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1,2-dichloorethaan</t>
+          <t>Dieldrin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1562,25 +1454,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>dieldn</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
-        <is>
-          <t>12DClC2a</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1588,26 +1475,26 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>75-09-2</t>
+          <t>330-54-1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DClC1a</t>
+          <t>Durn</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dichloormethaan</t>
+          <t>diuron</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dichloormethaan</t>
+          <t>Diuron</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1617,25 +1504,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Durn</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
-        <is>
-          <t>DClC1a</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1643,26 +1525,26 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>62-73-7</t>
+          <t>959-98-8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DClvs</t>
+          <t>aedsfn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>dichloorvos</t>
+          <t>alfa-endosulfan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>dichloorvos</t>
+          <t>alfa-Endosulfan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1672,25 +1554,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>aedsfn</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
-        <is>
-          <t>DClvs</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1698,69 +1575,76 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>115-32-2</t>
+          <t>33213-65-9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dcfl</t>
+          <t>bedsfn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dicofol</t>
+          <t>beta-endosulfan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dicofol</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+          <t>beta-Endosulfan</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CONCTTE</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>bedsfn</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dcfl</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>60-57-1</t>
+          <t>72-20-8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dieldn</t>
+          <t>endn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dieldrin</t>
+          <t>endrin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dieldrin</t>
+          <t>Endrin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1770,25 +1654,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>endn</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
-        <is>
-          <t>dieldn</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -1796,26 +1675,26 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1177</v>
+        <v>1191</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>330-54-1</t>
+          <t>206-44-0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Durn</t>
+          <t>Flu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>diuron</t>
+          <t>fluorantheen</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Diuron</t>
+          <t>Fluorantheen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1825,52 +1704,47 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Flu</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Durn</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1177</v>
+        <v>1197</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>330-54-1</t>
+          <t>76-44-8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Durn</t>
+          <t>HpCl</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>diuron</t>
+          <t>heptachloor</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Diuron</t>
+          <t>heptachloor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1880,52 +1754,47 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>HpCl</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Durn</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1178</v>
+        <v>1198</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>959-98-8</t>
+          <t>1024-57-3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>aedsfn</t>
+          <t>cHpClepO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>alfa-endosulfan</t>
+          <t>cis-heptachloorepoxide</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>alfa-Endosulfan</t>
+          <t>heptachloorepoxide</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1935,52 +1804,47 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>cHpClepO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>aedsfn</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1179</v>
+        <v>1199</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33213-65-9</t>
+          <t>118-74-1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bedsfn</t>
+          <t>HCB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>beta-endosulfan</t>
+          <t>hexachloorbenzeen</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>beta-Endosulfan</t>
+          <t>Hexachloorbenzeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1990,52 +1854,47 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>HCB</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bedsfn</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>72-20-8</t>
+          <t>319-84-6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>endn</t>
+          <t>aHCH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>endrin</t>
+          <t>alfa-hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Endrin</t>
+          <t>alpha Hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2045,25 +1904,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>aHCH</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
-        <is>
-          <t>endn</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2071,26 +1925,26 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1181</v>
+        <v>1201</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>72-20-8</t>
+          <t>319-85-7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>endn</t>
+          <t>bHCH</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>endrin</t>
+          <t>beta-hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Endrin</t>
+          <t>beta Hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2100,25 +1954,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>bHCH</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
-        <is>
-          <t>endn</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2126,26 +1975,26 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1191</v>
+        <v>1202</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>206-44-0</t>
+          <t>319-86-8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Flu</t>
+          <t>dHCH</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>fluorantheen</t>
+          <t>delta-hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fluorantheen</t>
+          <t>delta Hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2155,52 +2004,47 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>dHCH</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Flu</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1191</v>
+        <v>1203</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>206-44-0</t>
+          <t>58-89-9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Flu</t>
+          <t>cHCH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>fluorantheen</t>
+          <t>gamma-hexachloorcyclohexaan (lindaan)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fluorantheen</t>
+          <t>gamma Hexachloorcyclohexaan (Lindaan)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2210,52 +2054,47 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>cHCH</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Flu</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>76-44-8</t>
+          <t>193-39-5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HpCl</t>
+          <t>InP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>heptachloor</t>
+          <t>indeno(1,2,3-cd)pyreen</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>heptachloor</t>
+          <t>Indeno (123cd) pyreen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2265,25 +2104,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>InP</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
-        <is>
-          <t>HpCl</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
         <is>
           <t>OPGLT</t>
         </is>
@@ -2291,26 +2125,26 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1198</v>
+        <v>1207</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1024-57-3</t>
+          <t>465-73-6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cHpClepO</t>
+          <t>idn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cis-heptachloorepoxide</t>
+          <t>isodrin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>heptachloorepoxide</t>
+          <t>Isodrin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2320,52 +2154,47 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>idn</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>cHpClepO</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>118-74-1</t>
+          <t>34123-59-6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HCB</t>
+          <t>iptrn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>hexachloorbenzeen</t>
+          <t>isoproturon</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hexachloorbenzeen</t>
+          <t>Isoproturon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2375,52 +2204,47 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>iptrn</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>HCB</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1200</v>
+        <v>1235</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>319-84-6</t>
+          <t>87-86-5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>aHCH</t>
+          <t>PeClFol</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>alfa-hexachloorcyclohexaan</t>
+          <t>pentachloorfenol</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>alpha Hexachloorcyclohexaan</t>
+          <t>Pentachloorfenol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2430,25 +2254,20 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PeClFol</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
-        <is>
-          <t>aHCH</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2456,26 +2275,26 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1201</v>
+        <v>1263</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>319-85-7</t>
+          <t>122-34-9</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bHCH</t>
+          <t>simzne</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>beta-hexachloorcyclohexaan</t>
+          <t>simazine</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>beta Hexachloorcyclohexaan</t>
+          <t>Simazine</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2485,25 +2304,20 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>simzne</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
-        <is>
-          <t>bHCH</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2511,26 +2325,26 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1202</v>
+        <v>1269</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>319-86-8</t>
+          <t>886-50-0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dHCH</t>
+          <t>terbtn</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>delta-hexachloorcyclohexaan</t>
+          <t>terbutrin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>delta Hexachloorcyclohexaan</t>
+          <t>Terbutryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2540,25 +2354,20 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>terbtn</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
-        <is>
-          <t>dHCH</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2566,26 +2375,26 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1202</v>
+        <v>1272</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>319-86-8</t>
+          <t>127-18-4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dHCH</t>
+          <t>T4ClC2e</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>delta-hexachloorcyclohexaan</t>
+          <t>tetrachlooretheen (per)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>delta Hexachloorcyclohexaan</t>
+          <t>Tetrachlooreth(yl)een</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2595,25 +2404,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>T4ClC2e</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
-        <is>
-          <t>dHCH</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2621,26 +2425,26 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1203</v>
+        <v>1276</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>58-89-9</t>
+          <t>56-23-5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cHCH</t>
+          <t>T4ClC1a</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>gamma-hexachloorcyclohexaan (lindaan)</t>
+          <t>tetrachloormethaan (tetra)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>gamma Hexachloorcyclohexaan (Lindaan)</t>
+          <t>Tetrachloormethaan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2650,25 +2454,20 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>T4ClC1a</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
-        <is>
-          <t>cHCH</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2676,26 +2475,26 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1203</v>
+        <v>1283</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>58-89-9</t>
+          <t>120-82-1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>cHCH</t>
+          <t>124TClBen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>gamma-hexachloorcyclohexaan (lindaan)</t>
+          <t>1,2,4-trichloorbenzeen</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>gamma Hexachloorcyclohexaan (Lindaan)</t>
+          <t>1,2,4 Trichloorbenzeen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2705,25 +2504,20 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>124TClBen</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
-        <is>
-          <t>cHCH</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -2731,26 +2525,26 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1204</v>
+        <v>1286</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>193-39-5</t>
+          <t>79-01-6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>InP</t>
+          <t>TClC2e</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>indeno(1,2,3-cd)pyreen</t>
+          <t>trichlooretheen (tri)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Indeno (123cd) pyreen</t>
+          <t>Trichlooreth(yl)een</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2760,52 +2554,47 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>TClC2e</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>InP</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1204</v>
+        <v>1289</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>193-39-5</t>
+          <t>1582-09-8</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>InP</t>
+          <t>Tfrlne</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>indeno(1,2,3-cd)pyreen</t>
+          <t>trifluraline</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Indeno (123cd) pyreen</t>
+          <t>Trifluraline</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2815,52 +2604,47 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Tfrlne</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>InP</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1207</v>
+        <v>1337</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>465-73-6</t>
+          <t>16887-00-6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>idn</t>
+          <t>Cl</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>isodrin</t>
+          <t>chloride</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Isodrin</t>
+          <t>Chloride</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2870,52 +2654,47 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Cl</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>idn</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1207</v>
+        <v>1339</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>465-73-6</t>
+          <t>14797-65-0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>idn</t>
+          <t>NO2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>isodrin</t>
+          <t>nitriet</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Isodrin</t>
+          <t>Nitriet NO2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2925,80 +2704,70 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>mg/L N</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>NO2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>idn</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>Nnf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1208</v>
+        <v>1369</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>34123-59-6</t>
+          <t>7440-38-2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>iptrn</t>
+          <t>As</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>isoproturon</t>
+          <t>arseen</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Isoproturon</t>
+          <t>Arseen  opgelost</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>As</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
-        <is>
-          <t>iptrn</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -3006,109 +2775,99 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1208</v>
+        <v>1369</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>34123-59-6</t>
+          <t>7440-38-2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>iptrn</t>
+          <t>As</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>isoproturon</t>
+          <t>arseen</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Isoproturon</t>
+          <t>Arseen  opgelost</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>As</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>iptrn</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1235</v>
+        <v>1379</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>87-86-5</t>
+          <t>7440-38-2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PeClFol</t>
+          <t>As</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>pentachloorfenol</t>
+          <t>arseen</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pentachloorfenol</t>
+          <t>kobalt opgelost</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>As</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
-        <is>
-          <t>PeClFol</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -3116,109 +2875,99 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1263</v>
+        <v>1379</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>122-34-9</t>
+          <t>7440-38-2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>simzne</t>
+          <t>As</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>simazine</t>
+          <t>arseen</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Simazine</t>
+          <t>kobalt opgelost</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>As</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>simzne</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1263</v>
+        <v>1382</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>122-34-9</t>
+          <t>7439-92-1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>simzne</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>simazine</t>
+          <t>lood</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Simazine</t>
+          <t>Lood (Pb) opgelost</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
-        <is>
-          <t>simzne</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -3226,109 +2975,99 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1269</v>
+        <v>1382</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>886-50-0</t>
+          <t>7439-92-1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>terbtn</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>terbutrin</t>
+          <t>lood</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Terbutryne</t>
+          <t>Lood (Pb) opgelost</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Pb</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>terbtn</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1272</v>
+        <v>1386</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>127-18-4</t>
+          <t>7440-02-0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>T4ClC2e</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tetrachlooretheen (per)</t>
+          <t>nikkel</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tetrachlooreth(yl)een</t>
+          <t>Nikkel (Ni) opgelost</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
-        <is>
-          <t>T4ClC2e</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -3336,164 +3075,149 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1276</v>
+        <v>1386</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>56-23-5</t>
+          <t>7440-02-0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>T4ClC1a</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tetrachloormethaan (tetra)</t>
+          <t>nikkel</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tetrachloormethaan</t>
+          <t>Nikkel (Ni) opgelost</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>T4ClC1a</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1283</v>
+        <v>1387</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>120-82-1</t>
+          <t>7439-97-6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>124TClBen</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1,2,4-trichloorbenzeen</t>
+          <t>kwik</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1,2,4 Trichloorbenzeen</t>
+          <t>Kwik (Hg) opgelost</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>124TClBen</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1286</v>
+        <v>1387</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>79-01-6</t>
+          <t>7439-97-6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TClC2e</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>trichlooretheen (tri)</t>
+          <t>kwik</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trichlooreth(yl)een</t>
+          <t>Kwik (Hg) opgelost</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Hg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
-        <is>
-          <t>TClC2e</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -3501,26 +3225,26 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1289</v>
+        <v>1388</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1582-09-8</t>
+          <t>7440-43-9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tfrlne</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>trifluraline</t>
+          <t>cadmium</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trifluraline</t>
+          <t>Cadmium (Cd) opgelost</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3530,25 +3254,20 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
-        <is>
-          <t>Tfrlne</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -3556,26 +3275,26 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1337</v>
+        <v>1388</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16887-00-6</t>
+          <t>7440-43-9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cl</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>chloride</t>
+          <t>cadmium</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chloride</t>
+          <t>Cadmium (Cd) opgelost</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3585,25 +3304,20 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
-        <is>
-          <t>Cl</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
         <is>
           <t>nf</t>
         </is>
@@ -3611,136 +3325,126 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1339</v>
+        <v>1388</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14797-65-0</t>
+          <t>7440-43-9</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NO2</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>nitriet</t>
+          <t>cadmium</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nitriet NO2</t>
+          <t>Cadmium (Cd) opgelost</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NO2</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Nnf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1339</v>
+        <v>1388</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14797-65-0</t>
+          <t>7440-43-9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NO2</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>nitriet</t>
+          <t>cadmium</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nitriet NO2</t>
+          <t>Cadmium (Cd) opgelost</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>mg/L N</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Cd</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>NO2</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Nnf</t>
+          <t>nf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1369</v>
+        <v>1392</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>7440-50-8</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>koper</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Arseen  opgelost</t>
+          <t>koper (Cu) opgelost</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3750,25 +3454,20 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -3776,26 +3475,26 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1369</v>
+        <v>1392</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>7440-50-8</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>koper</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Arseen  opgelost</t>
+          <t>koper (Cu) opgelost</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3805,25 +3504,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Cu</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
         <is>
           <t>nf</t>
         </is>
@@ -3831,26 +3525,26 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1369</v>
+        <v>1433</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>14265-44-2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>fosfaat</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Arseen  opgelost</t>
+          <t>Opgeloste orthofosfaten</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3860,245 +3554,220 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>mg/L P</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PO4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>Pnf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1369</v>
+        <v>1439</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>479-61-8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>CHLFa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>chlorofyl-a</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arseen  opgelost</t>
+          <t>Chlorofyl a</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>CHLFa</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1379</v>
+        <v>1458</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>120-12-7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>antraceen</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>kobalt opgelost</t>
+          <t>Antraceen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1379</v>
+        <v>1464</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7440-38-2</t>
+          <t>470-90-6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Clfvfs</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>arseen</t>
+          <t>chloorfenvinfos</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>kobalt opgelost</t>
+          <t>Chloorfenvinfos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Clfvfs</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1382</v>
+        <v>1517</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7439-92-1</t>
+          <t>91-20-3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>Naf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>naftaleen</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lood (Pb) opgelost</t>
+          <t>Naftaleen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>Naf</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
-        <is>
-          <t>Pb</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -4106,109 +3775,99 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1382</v>
+        <v>1629</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7439-92-1</t>
+          <t>108-70-3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>135TClBen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>1,3,5-trichloorbenzeen</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lood (Pb) opgelost</t>
+          <t>1,3,5 Trichloorbenzeen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>135TClBen</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Pb</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1382</v>
+        <v>1630</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7439-92-1</t>
+          <t>87-61-6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>123TClBen</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>1,2,3-trichloorbenzeen</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lood (Pb) opgelost</t>
+          <t>1,2,3 Trichloorbenzeen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>123TClBen</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
-        <is>
-          <t>Pb</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -4216,109 +3875,99 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1382</v>
+        <v>1652</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7439-92-1</t>
+          <t>87-68-3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pb</t>
+          <t>HxClbtDen</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>lood</t>
+          <t>hexachloorbutadieen</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lood (Pb) opgelost</t>
+          <t>Hexachloorbutadieen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>HxClbtDen</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Pb</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1386</v>
+        <v>1688</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7440-02-0</t>
+          <t>74070-46-5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>acnfn</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>aclonifen</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nikkel (Ni) opgelost</t>
+          <t>aclonifen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>acnfn</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
-        <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -4326,109 +3975,99 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1386</v>
+        <v>1877</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7440-02-0</t>
+          <t>138261-41-3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>imdcpd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>imidacloprid</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nikkel (Ni) opgelost</t>
+          <t>imidacloprid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>imdcpd</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1386</v>
+        <v>1888</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7440-02-0</t>
+          <t>608-93-5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>PeClBen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>pentachloorbenzeen</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nikkel (Ni) opgelost</t>
+          <t>Pentachloorbenzeen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PeClBen</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
-        <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -4436,164 +4075,149 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1386</v>
+        <v>1935</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7440-02-0</t>
+          <t>28159-98-0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>irgrl</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>nikkel</t>
+          <t>irgarol</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nikkel (Ni) opgelost</t>
+          <t>cybutryne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>irgrl</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1387</v>
+        <v>1959</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7439-97-6</t>
+          <t>140-66-9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hg</t>
+          <t>4ttC8yFol</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>kwik</t>
+          <t>4-tertiair-octylfenol</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kwik (Hg) opgelost</t>
+          <t>4-(1,1',3,3' - tetramethylbutyl)-fenol (Para-tert-octylfenol)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>4ttC8yFol</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Hg</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1387</v>
+        <v>2028</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7439-97-6</t>
+          <t>124495-18-7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hg</t>
+          <t>quinoxfn</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>kwik</t>
+          <t>quinoxyfen</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kwik (Hg) opgelost</t>
+          <t>Quinoxyfen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>quinoxfn</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
-        <is>
-          <t>Hg</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -4601,26 +4225,26 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1388</v>
+        <v>2879</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>36643-28-4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>TC4ySn</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>tributyltin (kation)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
+          <t>Verbindingen van tributyltin (Tributyltin kation)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4630,25 +4254,20 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>TC4ySn</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
-        <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -4656,576 +4275,478 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1388</v>
+        <v>2911</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>207122-15-4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>PBDE154</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>2,2',4,4',5,6'-hexabroomdifenylether</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>PBDE154 (2,2',4,4',5,6'-hexabroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PBDE154</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1388</v>
+        <v>2912</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>68631-49-2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>PBDE153</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>2,2',4,4',5,5'-hexabroomdifenylether</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>PBDE153 (2,2',4,4',5,5'-hexabroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PBDE153</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1388</v>
+        <v>2915</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>189084-64-8</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>PBDE100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>2,2',4,4',6-pentabroomdifenylether</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>PBDE100 (2,2',4,4',6-pentabroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PBDE100</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1388</v>
+        <v>2916</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>60348-60-9</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>PBDE99</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>2,2',4,4',5-pentabroomdifenylether</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
+          <t>PBDE99 (2,2',4,4',5-pentabroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PBDE99</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1388</v>
+        <v>2919</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7440-43-9</t>
+          <t>5436-43-1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cd</t>
+          <t>PBDE47</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>cadmium</t>
+          <t>2,2',4,4'-tetrabroomdifenylether</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cadmium (Cd) opgelost</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
+          <t>PBDE47 (2,2',4,4'-tetrabroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PBDE47</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Cd</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1392</v>
+        <v>2920</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7440-50-8</t>
+          <t>41318-75-6</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>PBDE28</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>2,4,4'-tribroomdifenylether</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>koper (Cu) opgelost</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>PBDE28 (2,4,4'-tribroomdifenylether)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PBDE28</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1392</v>
+        <v>5347</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7440-50-8</t>
+          <t>335-67-1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>perfluoroctaanzuur</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>koper (Cu) opgelost</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1392</v>
+        <v>5978</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7440-50-8</t>
+          <t>307-24-4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>perfluorhexaanzuur</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>koper (Cu) opgelost</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1392</v>
+        <v>5979</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7440-50-8</t>
+          <t>2706-90-3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cu</t>
+          <t>PFPA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>koper</t>
+          <t>perfluorpentaanzuur</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>koper (Cu) opgelost</t>
+          <t>PFPeA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>PFPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>nf</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1433</v>
+        <v>6616</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>14265-44-2</t>
+          <t>117-81-7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PO4</t>
+          <t>DEHP</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>fosfaat</t>
+          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Opgeloste orthofosfaten</t>
+          <t>Di(2-ethylhexyl)ftalaat DEHP</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>mg/L P</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>DEHP</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>PO4</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Pnf</t>
+          <t>NVT</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1439</v>
+        <v>6830</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>479-61-8</t>
+          <t>355-46-4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CHLFa</t>
+          <t>L_PFHxS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>chlorofyl-a</t>
+          <t>perfluorhexaansulfonzuur</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chlorofyl a</t>
+          <t>PFHxS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5235,1988 +4756,70 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>µg/L</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>L_PFHxS</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>CHLFa</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>NVT</t>
+          <t>OPGLT</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1439</v>
+        <v>7073</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>479-61-8</t>
+          <t>16984-48-8</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CHLFa</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>chlorofyl-a</t>
+          <t>fluoride</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chlorofyl a</t>
+          <t>Anorganische fluoriden = fluoride opgelost</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>µg/L</t>
+          <t>CONCTTE</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CONCTTE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
-        <is>
-          <t>CHLFa</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>1458</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>120-12-7</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ant</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>antraceen</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Antraceen</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Ant</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>1458</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>120-12-7</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ant</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>antraceen</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Antraceen</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Ant</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>1464</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>470-90-6</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Clfvfs</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>chloorfenvinfos</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Chloorfenvinfos</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Clfvfs</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>1517</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>91-20-3</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Naf</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>naftaleen</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Naftaleen</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Naf</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>1517</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>91-20-3</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Naf</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>naftaleen</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Naftaleen</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Naf</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>1629</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>108-70-3</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>135TClBen</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1,3,5-trichloorbenzeen</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>1,3,5 Trichloorbenzeen</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>135TClBen</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>1630</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>87-61-6</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>123TClBen</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>1,2,3-trichloorbenzeen</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>1,2,3 Trichloorbenzeen</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>123TClBen</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>1652</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>87-68-3</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>HxClbtDen</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>hexachloorbutadieen</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Hexachloorbutadieen</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>HxClbtDen</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>1688</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>74070-46-5</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>acnfn</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>aclonifen</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>aclonifen</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>acnfn</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>1688</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>74070-46-5</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>acnfn</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>aclonifen</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>aclonifen</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>acnfn</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>1877</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>138261-41-3</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>imdcpd</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>imidacloprid</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>imidacloprid</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>imdcpd</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>1877</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>138261-41-3</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>imdcpd</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>imidacloprid</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>imidacloprid</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>imdcpd</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>1888</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>608-93-5</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>PeClBen</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>pentachloorbenzeen</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Pentachloorbenzeen</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>PeClBen</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>28159-98-0</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>irgrl</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>irgarol</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>cybutryne</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>irgrl</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>140-66-9</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>4ttC8yFol</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4-tertiair-octylfenol</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>4-(1,1',3,3' - tetramethylbutyl)-fenol (Para-tert-octylfenol)</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>4ttC8yFol</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>124495-18-7</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>quinoxfn</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>quinoxyfen</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Quinoxyfen</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>quinoxfn</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>2879</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>36643-28-4</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>TC4ySn</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>tributyltin (kation)</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Verbindingen van tributyltin (Tributyltin kation)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>TC4ySn</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>2879</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>36643-28-4</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>TC4ySn</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>tributyltin (kation)</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Verbindingen van tributyltin (Tributyltin kation)</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>TC4ySn</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>2911</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>207122-15-4</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>PBDE154</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2,2',4,4',5,6'-hexabroomdifenylether</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>PBDE154 (2,2',4,4',5,6'-hexabroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>PBDE154</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>2912</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>68631-49-2</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>PBDE153</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2,2',4,4',5,5'-hexabroomdifenylether</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>PBDE153 (2,2',4,4',5,5'-hexabroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>PBDE153</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>2915</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>189084-64-8</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>PBDE100</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2,2',4,4',6-pentabroomdifenylether</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>PBDE100 (2,2',4,4',6-pentabroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>PBDE100</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>2916</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>60348-60-9</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>PBDE99</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2,2',4,4',5-pentabroomdifenylether</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>PBDE99 (2,2',4,4',5-pentabroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>PBDE99</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>2919</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>5436-43-1</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>PBDE47</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2,2',4,4'-tetrabroomdifenylether</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>PBDE47 (2,2',4,4'-tetrabroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>PBDE47</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>2920</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>41318-75-6</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>PBDE28</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2,4,4'-tribroomdifenylether</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>PBDE28 (2,4,4'-tribroomdifenylether)</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>PBDE28</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>5347</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>335-67-1</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>perfluoroctaanzuur</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>5347</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>335-67-1</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>perfluoroctaanzuur</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>PFOA</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>5978</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>307-24-4</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>PFHxA</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>perfluorhexaanzuur</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>PFHxA</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>PFHxA</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>5978</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>307-24-4</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>PFHxA</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>perfluorhexaanzuur</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>PFHxA</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>PFHxA</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>5979</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2706-90-3</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>PFPA</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>perfluorpentaanzuur</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>PFPeA</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>PFPA</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>5979</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2706-90-3</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>PFPA</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>perfluorpentaanzuur</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>PFPeA</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>PFPA</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>6616</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>117-81-7</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>DEHP</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Di(2-ethylhexyl)ftalaat DEHP</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>DEHP</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>6616</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>117-81-7</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>DEHP</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>bis(2-ethylhexyl)ftalaat (DEHP)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Di(2-ethylhexyl)ftalaat DEHP</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>DEHP</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>6830</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>355-46-4</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>L_PFHxS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>perfluorhexaansulfonzuur</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>PFHxS</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>L_PFHxS</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>6830</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>355-46-4</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>L_PFHxS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>perfluorhexaansulfonzuur</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>PFHxS</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>L_PFHxS</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>OPGLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>7073</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>16984-48-8</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>fluoride</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Anorganische fluoriden = fluoride opgelost</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>7073</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>16984-48-8</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>fluoride</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Anorganische fluoriden = fluoride opgelost</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>CONCTTE</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
@@ -7233,7 +4836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7269,25 +4872,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Aanpak kwantificeringsgrens</t>
+          <t>Unieke identificatie van de eenheid</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Unieke identificatie van de eenheid</t>
+          <t>grootheid_code</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>grootheid_code</t>
+          <t>wadar_PARCode</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>wadar_PARCode</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hoedanigheid_code</t>
         </is>
@@ -7312,28 +4910,35 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1082</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+        <v>1116</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>205-99-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BbF</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>benzo(b)fluorantheen</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Benzo(a)antraceen</t>
+          <t>Benzo (b) fluorantheen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7343,40 +4948,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1116</v>
+        <v>1143</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>205-99-2</t>
+          <t>53-19-0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BbF</t>
+          <t>24DDD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>benzo(b)fluorantheen</t>
+          <t>2,4'-dichloordifenyldichloorethaan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Benzo (b) fluorantheen</t>
+          <t>DDD op'</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7386,40 +4986,35 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1116</v>
+        <v>1145</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>205-99-2</t>
+          <t>3424-82-6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BbF</t>
+          <t>24DDE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>benzo(b)fluorantheen</t>
+          <t>2,4'-dichloordifenyldichlooretheen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Benzo (b) fluorantheen</t>
+          <t>DDE op'</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7429,40 +5024,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1143</v>
+        <v>1301</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>53-19-0</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>24DDD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2,4'-dichloordifenyldichloorethaan</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DDD op'</t>
+          <t>Watertemperatuur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7472,40 +5054,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1145</v>
+        <v>1302</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3424-82-6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>24DDE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2,4'-dichloordifenyldichlooretheen</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DDE op'</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7515,21 +5084,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>u pH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -7540,7 +5104,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Watertemperatuur</t>
+          <t>Geleidbaarheid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7550,21 +5114,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
+          <t>µS/cm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -7575,7 +5134,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Zwevende stoffen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7585,91 +5144,60 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>u pH</t>
-        </is>
-      </c>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80937-33-3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Geleidbaarheid</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>µS/cm</t>
-        </is>
-      </c>
+          <t>Opgeloste zuurstof</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80937-33-3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zwevende stoffen</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
+          <t>Opgeloste zuurstof</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -7680,7 +5208,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zwevende stoffen</t>
+          <t>BZV5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7690,78 +5218,87 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
+          <t>mgO2/L</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>80937-33-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Opgeloste zuurstof</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>CZV</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>mgO2/L</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80937-33-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Opgeloste zuurstof</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>Kjeldahl stikstof</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>mg/L N</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1313</v>
+        <v>1335</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6684-80-6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BZV5</t>
+          <t>Ammonium NH4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -7771,32 +5308,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>mgO2/L</t>
-        </is>
-      </c>
+          <t>mg/L N</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1313</v>
+        <v>1338</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18785-72-3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BZV5</t>
+          <t>Sulfaat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7806,32 +5338,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>mgO2/L</t>
-        </is>
-      </c>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1314</v>
+        <v>1340</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>84145-82-4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CZV</t>
+          <t>Nitraat NO3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -7841,21 +5368,16 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>mgO2/L</t>
-        </is>
-      </c>
+          <t>mg/L N</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1314</v>
+        <v>1345</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -7866,7 +5388,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CZV</t>
+          <t>Hardheid TH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -7876,21 +5398,16 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>mgO2/L</t>
-        </is>
-      </c>
+          <t>°F</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1319</v>
+        <v>1350</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -7901,7 +5418,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kjeldahl stikstof</t>
+          <t>Totaal fosfor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -7911,172 +5428,143 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>mg/L N</t>
-        </is>
-      </c>
+          <t>mg/L P</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1319</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>1361</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kjeldahl stikstof</t>
+          <t>Uraan (U) opgelost</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>mg/L N</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1335</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>6684-80-6</t>
-        </is>
-      </c>
+        <v>1368</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ammonium NH4</t>
+          <t>Zilver (Ag) opgelost</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>mg/L N</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1335</v>
+        <v>1383</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6684-80-6</t>
+          <t>9029-97-4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ammonium NH4</t>
+          <t>Zink (Zn) opgelost</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>mg/L N</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1338</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>18785-72-3</t>
-        </is>
-      </c>
+        <v>1385</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sulfaat</t>
+          <t>Seleen (Se) opgelost</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>nf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1340</v>
+        <v>1551</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>84145-82-4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>7727-37-9</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>distikstof</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nitraat NO3</t>
+          <t>Totaal stikstof (Kj + NO2 + NO3)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -8086,32 +5574,35 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
           <t>mg/L N</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1340</v>
+        <v>1743</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>84145-82-4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>115-29-7</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>endsfn</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>endosulfan (som alfa- en beta-isomeer)</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nitraat NO3</t>
+          <t>Endosulfan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8121,32 +5612,35 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>mg/L N</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1345</v>
+        <v>1774</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+          <t>12002-48-1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TClBen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>trichloorbenzeen</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hardheid TH</t>
+          <t>Trichloorbenzenen (alle isomeren)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8156,522 +5650,443 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>°F</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1350</v>
+        <v>1920</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>1806-26-4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4C8yFol</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4-n-octylfenol</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Totaal fosfor</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>mg/L P</t>
-        </is>
-      </c>
+          <t>Octylfenolen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1361</v>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+        <v>1955</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>85535-84-8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sC10C13Clakn</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>som C10-C13-chlooralkanen</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Uraan (U) opgelost</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>C10-C13-chlooralkanen</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1361</v>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+        <v>1958</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>104-40-5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4C9yFol</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4-nonylfenol</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Uraan (U) opgelost</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>4-nonylfenol</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1368</v>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+        <v>5474</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>25154-52-3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C9yFol</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nonylfenol</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zilver (Ag) opgelost</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Nonylfenolen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1383</v>
+        <v>5534</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9029-97-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zink (Zn) opgelost</t>
+          <t>Som aldrin+endrin+dieldrin+isodrin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1383</v>
+        <v>5537</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9029-97-4</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>608-73-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sHCH</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>som hexachloorcyclohexaan-isomeren</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zink (Zn) opgelost</t>
+          <t>Hexachloorcyclohexaan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1385</v>
+        <v>5977</v>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Seleen (Se) opgelost</t>
+          <t xml:space="preserve"> PFHpA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1385</v>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+        <v>6561</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1763-23-1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PFOS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>perfluoroctaansulfonzuur</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Seleen (Se) opgelost</t>
+          <t>Perfluor octaanzuur PFOS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>nf</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1551</v>
+        <v>6678</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7727-37-9</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>N2</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>distikstof</t>
-        </is>
-      </c>
+          <t>32534-81-9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Totaal stikstof (Kj + NO2 + NO3)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>mg/L N</t>
-        </is>
-      </c>
+          <t>Pentabroomdifenylether som</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1743</v>
+        <v>6678</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>115-29-7</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>endsfn</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>endosulfan (som alfa- en beta-isomeer)</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Endosulfan</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>polybroomdifenylether, totaal</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1774</v>
+        <v>7128</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12002-48-1</t>
+          <t>3194-55-6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TClBen</t>
+          <t>sHBCD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>trichloorbenzeen</t>
+          <t>som 1,2,5,6,9,10-hexabroomcyclododecaan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trichloorbenzenen (alle isomeren)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>hexabroom-cyclododecaan (HBCDD)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1920</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1806-26-4</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>4C8yFol</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>4-n-octylfenol</t>
-        </is>
-      </c>
+        <v>7170</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Octylfenolen</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t xml:space="preserve">Som DDT 2,4' &amp; 4,4', DDD 2,4' &amp; 4,4'  DDE 2,4' &amp; 4,4' </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1955</v>
+        <v>7706</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>85535-84-8</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>sC10C13Clakn</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>som C10-C13-chlooralkanen</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>C10-C13-chlooralkanen</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>Heptachloor + heptachloorepoxide</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>1958</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>104-40-5</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>4C9yFol</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>4-nonylfenol</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4-nonylfenol</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+          <t>Opgeloste organische koolstof DOC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>nf</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>5474</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>COT</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>25154-52-3</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>C9yFol</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>nonylfenol</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nonylfenolen</t>
+          <t>Totaal organische koolstof TOC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -8679,248 +6094,144 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>5534</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DIAT</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EEA_124-04-9 *</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Som aldrin+endrin+dieldrin+isodrin</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Evaluatie biologische kwaliteit - Diatomeeën</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>5537</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FISH</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>608-73-1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>sHCH</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>som hexachloorcyclohexaan-isomeren</t>
-        </is>
-      </c>
+          <t>EEA_14-02-8 *</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hexachloorcyclohexaan</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Evaluatie biologische kwaliteit -Vis</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>5977</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>IBGA</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PFHpA </t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>5977</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IBGN</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PFHpA </t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>6561</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>INV</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1763-23-1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>PFOS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>perfluoroctaansulfonzuur</t>
-        </is>
-      </c>
+          <t>EEA_13-01-4 *</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Perfluor octaanzuur PFOS</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>Evaluatie biologische kwaliteit - Macro-invertebraten</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>6561</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1763-23-1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PFOS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>perfluoroctaansulfonzuur</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unieke identificatie gemeten parameter
+Sandre code</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Perfluor octaanzuur PFOS</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
+          <t>PARAMETER</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>6678</v>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>32534-81-9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pentabroomdifenylether som</t>
+          <t>Dioxines en verbindingen van het dioxinetype</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -8928,354 +6239,18 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>6678</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>polybroomdifenylether, totaal</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>7128</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3194-55-6</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>sHBCD</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>som 1,2,5,6,9,10-hexabroomcyclododecaan</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>hexabroom-cyclododecaan (HBCDD)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>7170</v>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Som DDT 2,4' &amp; 4,4', DDD 2,4' &amp; 4,4'  DDE 2,4' &amp; 4,4' </t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>7706</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Heptachloor + heptachloorepoxide</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Opgeloste organische koolstof DOC</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>nf</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>COT</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Totaal organische koolstof TOC</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>DIAT</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>EEA_124-04-9 *</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Evaluatie biologische kwaliteit - Diatomeeën</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>FISH</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>EEA_14-02-8 *</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Evaluatie biologische kwaliteit -Vis</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>IBGA</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>IBGN</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>INV</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>EEA_13-01-4 *</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Evaluatie biologische kwaliteit - Macro-invertebraten</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Unieke identificatie gemeten parameter
-Sandre code</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>PARAMETER</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Dioxines en verbindingen van het dioxinetype</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mappings/parameter_e_h_g.xlsx
+++ b/mappings/parameter_e_h_g.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,11 @@
           <t>hoedanigheid_code</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>eenheid_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -530,6 +535,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -580,6 +590,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -630,6 +645,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -680,6 +700,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -730,6 +755,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -777,7 +807,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -827,7 +862,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -877,7 +917,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -930,6 +975,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -980,6 +1030,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1030,6 +1085,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1080,6 +1140,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1130,6 +1195,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1180,6 +1250,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1230,6 +1305,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1280,6 +1360,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1330,6 +1415,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1380,6 +1470,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1419,7 +1514,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -1472,6 +1572,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1522,6 +1627,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1572,6 +1682,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1622,6 +1737,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1672,6 +1792,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1719,7 +1844,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1899,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1954,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -1869,7 +2009,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -1922,6 +2067,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1972,6 +2122,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2022,6 +2177,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2072,6 +2232,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2119,7 +2284,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -2172,6 +2342,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2222,6 +2397,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2272,6 +2452,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2322,6 +2507,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2372,6 +2562,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2422,6 +2617,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2472,6 +2672,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2522,6 +2727,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2572,6 +2782,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2622,6 +2837,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2672,6 +2892,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>mg/l</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2722,6 +2947,11 @@
           <t>Nnf</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>mg/l</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2772,6 +3002,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2822,6 +3057,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2872,6 +3112,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2922,6 +3167,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2972,6 +3222,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3022,6 +3277,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3072,6 +3332,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3122,6 +3387,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3172,6 +3442,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3222,6 +3497,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3272,6 +3552,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3322,6 +3607,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3372,6 +3662,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3422,6 +3717,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3472,6 +3772,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3522,6 +3827,11 @@
           <t>nf</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3572,6 +3882,11 @@
           <t>Pnf</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>mg/l</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3622,6 +3937,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3669,7 +3989,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -3722,6 +4047,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3772,6 +4102,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3822,6 +4157,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3872,6 +4212,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3919,7 +4264,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -3972,6 +4322,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4022,6 +4377,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4072,6 +4432,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4122,6 +4487,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4172,6 +4542,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4222,6 +4597,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4272,6 +4652,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ng/l</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4314,6 +4699,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4353,7 +4743,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4790,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4837,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4884,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4931,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4986,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4621,7 +5041,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4671,7 +5096,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4724,6 +5154,11 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ug/l</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4771,7 +5206,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>OPGLT</t>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>ug/l</t>
         </is>
       </c>
     </row>
@@ -4822,6 +5262,11 @@
       <c r="J89" t="inlineStr">
         <is>
           <t>NVT</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>mg/l</t>
         </is>
       </c>
     </row>
@@ -4836,7 +5281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4890,6 +5335,11 @@
           <t>hoedanigheid_code</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>eenheid_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4916,6 +5366,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4954,6 +5405,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4992,6 +5444,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5030,6 +5483,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5060,6 +5514,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5090,6 +5545,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5120,6 +5576,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5150,6 +5607,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5172,6 +5630,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5194,6 +5653,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5224,6 +5684,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5254,6 +5715,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5284,6 +5746,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5314,6 +5777,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5344,6 +5808,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5374,6 +5839,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5404,6 +5870,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5434,6 +5901,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5460,6 +5928,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5486,6 +5955,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5516,6 +5986,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5542,6 +6013,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5580,6 +6052,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5618,6 +6091,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5656,6 +6130,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5686,6 +6161,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5716,6 +6192,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5746,6 +6223,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5776,6 +6254,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5806,6 +6285,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5844,6 +6324,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5870,6 +6351,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5908,6 +6390,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5930,6 +6413,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5952,6 +6436,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5982,6 +6467,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6008,6 +6494,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6038,6 +6525,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6070,6 +6558,7 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6094,6 +6583,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6118,6 +6608,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6142,6 +6633,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6158,6 +6650,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6174,6 +6667,7 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6198,6 +6692,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6219,6 +6714,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -6239,6 +6735,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -6251,6 +6748,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
